--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +89,13 @@
       <color rgb="000B6B2F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A5A00"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +120,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -199,6 +209,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -32402,12 +32415,16 @@
           <t>S</t>
         </is>
       </c>
-      <c r="O4" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P4" s="16" t="inlineStr"/>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q4" s="16" t="inlineStr"/>
       <c r="R4" s="16" t="inlineStr">
         <is>
@@ -32415,7 +32432,11 @@
         </is>
       </c>
       <c r="S4" s="16" t="inlineStr"/>
-      <c r="T4" s="16" t="inlineStr"/>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <t>Le libellé de menu « Deux mondes » devient « Crèche &amp; primaire ». Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="108" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -32485,12 +32506,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O5" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P5" s="16" t="inlineStr"/>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q5" s="16" t="inlineStr"/>
       <c r="R5" s="16" t="inlineStr">
         <is>
@@ -32498,7 +32523,11 @@
         </is>
       </c>
       <c r="S5" s="16" t="inlineStr"/>
-      <c r="T5" s="16" t="inlineStr"/>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>Tarifs de la page d’accueil en euros (plus de TND). Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="108" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -32568,12 +32597,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O6" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q6" s="16" t="inlineStr"/>
       <c r="R6" s="16" t="inlineStr">
         <is>
@@ -32581,7 +32614,11 @@
         </is>
       </c>
       <c r="S6" s="16" t="inlineStr"/>
-      <c r="T6" s="16" t="inlineStr"/>
+      <c r="T6" s="16" t="inlineStr">
+        <is>
+          <t>core/src/locales.js : packs de pays. tunisia.js délègue au pack actif. La Tunisie reste le défaut, intacte. Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -32651,12 +32688,16 @@
           <t>XL</t>
         </is>
       </c>
-      <c r="O7" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P7" s="16" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q7" s="16" t="inlineStr"/>
       <c r="R7" s="16" t="inlineStr">
         <is>
@@ -32664,7 +32705,11 @@
         </is>
       </c>
       <c r="S7" s="16" t="inlineStr"/>
-      <c r="T7" s="16" t="inlineStr"/>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>Sélecteur de PAYS dans les paramètres (Tunisie/France/International) pilotant régions, pièce d’identité, cadre légal, devise. Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="108" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -32734,9 +32779,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O8" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>TRIAGED</t>
         </is>
       </c>
       <c r="P8" s="16" t="inlineStr"/>
@@ -32751,7 +32796,11 @@
           <t>DEF-003</t>
         </is>
       </c>
-      <c r="T8" s="16" t="inlineStr"/>
+      <c r="T8" s="16" t="inlineStr">
+        <is>
+          <t>Le défaut « rien ne change au clic » est corrigé (DEF-003 : les ancres défilent + état actif). Des PAGES routées séparées avec URL propres restent un chantier plus large (SEO), à décider.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="108" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -32912,12 +32961,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P10" s="16" t="inlineStr"/>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q10" s="16" t="inlineStr"/>
       <c r="R10" s="16" t="inlineStr">
         <is>
@@ -32925,7 +32978,11 @@
         </is>
       </c>
       <c r="S10" s="16" t="inlineStr"/>
-      <c r="T10" s="16" t="inlineStr"/>
+      <c r="T10" s="16" t="inlineStr">
+        <is>
+          <t>Formulaire de pré-inscription enrichi : famille complète, santé, adresse structurée avec pays. Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="108" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -32995,12 +33052,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr"/>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q11" s="16" t="inlineStr"/>
       <c r="R11" s="16" t="inlineStr">
         <is>
@@ -33008,7 +33069,11 @@
         </is>
       </c>
       <c r="S11" s="16" t="inlineStr"/>
-      <c r="T11" s="16" t="inlineStr"/>
+      <c r="T11" s="16" t="inlineStr">
+        <is>
+          <t>6 engagements datés et conservés. Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="108" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
@@ -33078,12 +33143,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q12" s="16" t="inlineStr"/>
       <c r="R12" s="16" t="inlineStr">
         <is>
@@ -33091,7 +33160,11 @@
         </is>
       </c>
       <c r="S12" s="16" t="inlineStr"/>
-      <c r="T12" s="16" t="inlineStr"/>
+      <c r="T12" s="16" t="inlineStr">
+        <is>
+          <t>Formulaire à étapes guidé par le niveau (crèche/maternelle/primaire). Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="108" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -33161,9 +33234,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="O13" s="22" t="inlineStr">
+        <is>
+          <t>TRIAGED</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr"/>
@@ -33180,7 +33253,7 @@
       </c>
       <c r="T13" s="16" t="inlineStr">
         <is>
-          <t>Porte désormais AUSSI le grief « la page ne rentre pas » sur grand écran : la mesure montre 0 débordement sur ordinateur, donc c'est du design, pas un défaut. Le débordement mobile réel a été corrigé (DEF-001, clos).</t>
+          <t>Le débordement mobile réel est corrigé (DEF-001). La refonte visuelle complète de l’écran de connexion reste un choix de design d’Othman.</t>
         </is>
       </c>
     </row>
@@ -33252,9 +33325,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="O14" s="22" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr"/>
@@ -33265,7 +33338,11 @@
         </is>
       </c>
       <c r="S14" s="16" t="inlineStr"/>
-      <c r="T14" s="16" t="inlineStr"/>
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <t>Mention « Tunisie » retirée de l’écran de connexion. La réécriture des accroches marketing relève d’un choix éditorial.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="108" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
@@ -33426,12 +33503,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P16" s="16" t="inlineStr"/>
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P16" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q16" s="16" t="inlineStr"/>
       <c r="R16" s="16" t="inlineStr">
         <is>
@@ -33439,7 +33520,11 @@
         </is>
       </c>
       <c r="S16" s="16" t="inlineStr"/>
-      <c r="T16" s="16" t="inlineStr"/>
+      <c r="T16" s="16" t="inlineStr">
+        <is>
+          <t>Fiche technique par école dans la console plateforme : ce qu’on a, « à collecter » pour le reste. Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="108" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -33600,9 +33685,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
@@ -33613,7 +33698,11 @@
         </is>
       </c>
       <c r="S18" s="16" t="inlineStr"/>
-      <c r="T18" s="16" t="inlineStr"/>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <t>Recherche du modèle de rôles (Direction vs Administration) en cours : document en préparation.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="108" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -33932,9 +34021,9 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="P22" s="16" t="inlineStr"/>
@@ -33945,7 +34034,11 @@
         </is>
       </c>
       <c r="S22" s="16" t="inlineStr"/>
-      <c r="T22" s="16" t="inlineStr"/>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t>Recherche des relations entre tous les rôles × niveaux en cours.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="108" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -34098,12 +34191,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O24" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr"/>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q24" s="16" t="inlineStr"/>
       <c r="R24" s="16" t="inlineStr">
         <is>
@@ -34111,7 +34208,11 @@
         </is>
       </c>
       <c r="S24" s="16" t="inlineStr"/>
-      <c r="T24" s="16" t="inlineStr"/>
+      <c r="T24" s="16" t="inlineStr">
+        <is>
+          <t>Grille de saisie des notes par classe, au clavier, moyennes en direct. Déployé.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n"/>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -34535,27 +34535,97 @@
       <c r="S27" s="16" t="inlineStr"/>
       <c r="T27" s="16" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
-      <c r="M28" s="16" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
-      <c r="R28" s="16" t="n"/>
-      <c r="S28" s="16" t="n"/>
-      <c r="T28" s="16" t="n"/>
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>CR-026</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>ERP architecture</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Analyse d’écart vs ERP éducatifs professionnels (+ priorités Golfe)</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>Étudier les références fournies (ERPNext/Odoo Education, SAP/NetSuite/Dynamics, ERP scolaires du commerce) et découvrir ce qu’on n’a pas encore bâti. Focus marché : Bahreïn/Qatar.</t>
+        </is>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>Savoir exactement ce qui manque pour vendre au Golfe, et distinguer un bloqueur d’un confort.</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>Tout le produit</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>docs/quality/gap-analysis.md</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>P1 - Immediate</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q28" s="16" t="inlineStr">
+        <is>
+          <t>CR-025 (Bible)</t>
+        </is>
+      </c>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t>LIVRÉ : docs/quality/gap-analysis.md — 3 axes de recherche synthétisés. TIER-1 bloqueurs Golfe : passerelle de paiement régionale, transport+GPS, facturation TVA, calendrier Hijri, reporting Ministère. + manques d’architecture (journal d’audit, isolation tenant, moteur de workflow, reporting à dimensions) et de modèle académique (Grading Scale, Programme›Cours, Assessment Plan, Fee Structure). Séquencement vers la vente au §6. Reporté dans la Bible.</t>
+        </is>
+      </c>
+      <c r="S28" s="16" t="inlineStr"/>
+      <c r="T28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n"/>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -33963,12 +33963,16 @@
           <t>XL</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P21" s="16" t="inlineStr"/>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q21" s="16" t="inlineStr"/>
       <c r="R21" s="16" t="inlineStr">
         <is>
@@ -33978,7 +33982,7 @@
       <c r="S21" s="16" t="inlineStr"/>
       <c r="T21" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+          <t>LIVRÉ. Deux départements réels et composables : RH (rh@alnour.tn) et Comptabilité (comptable@alnour.tn), chacun avec son périmètre, son tableau de bord, et un cloisonnement prouvé (route + nav + données serveur). admin reste le généraliste. La séparation « déposant≠approbateur » viendra avec le moteur de workflow.</t>
         </is>
       </c>
     </row>
@@ -34416,14 +34420,14 @@
           <t>XL</t>
         </is>
       </c>
-      <c r="O26" s="22" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr">
         <is>
-          <t>À PHASER</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Q26" s="16" t="inlineStr">
@@ -34439,7 +34443,7 @@
       <c r="S26" s="16" t="inlineStr"/>
       <c r="T26" s="16" t="inlineStr">
         <is>
-          <t>Couche LANGUE livrée avec CR-023 (languages par pays : primaire/secondaire). Reste la couche CURRICULUM (niveaux/matières/évaluation/terminologie par pays) = gros œuvre, à phaser marché par marché. Architecture prête : locales.js EST la couche de config par pays, un seul cœur.</t>
+          <t>LIVRÉ. Couche curriculum par pays : matières + barème (/20 Tunisie, /100 Golfe) + échelle de mentions, dans locales.js. La grille de notes affiche le bon barème selon le pays. Ajouter un pays = un objet curriculum de plus. La terminologie fine se peaufine par marché.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -32139,7 +32139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T144"/>
+  <dimension ref="A1:T149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -34802,7 +34802,7 @@
       </c>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="P30" s="16" t="inlineStr"/>
@@ -34811,7 +34811,7 @@
       <c r="S30" s="16" t="n"/>
       <c r="T30" s="16" t="inlineStr">
         <is>
-          <t>SPÉCIFIÉ 2026-07-23 : docs/quality/hr-accounting-module-spec.md §3 (recherche NetSuite/ERPNext/Focus/GCC). Séquencement §5. À construire un sous-module à la fois. Gap actuel : salaire mono-montant, pas de bulletin, pas de WPS/EOSB, pas d'organigramme.</t>
+          <t>Volet 1 livré 2026-07-25 (85fb30d) : salaire multi-composants, bulletin de paie, maker-checker.</t>
         </is>
       </c>
     </row>
@@ -37382,6 +37382,266 @@
       <c r="R144" s="16" t="n"/>
       <c r="S144" s="16" t="n"/>
       <c r="T144" s="16" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CR-030</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Produit réel</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Retirer le concept « démo » du produit</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>C'est un produit réel maintenant, pas une démonstration. Toute mention démo disparaît de l'interface (web + mobile).</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Tout le produit</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Livré 2026-07-25 : CTA « Essai gratuit », « École d'exemple », « Journée simulée » ; i18n AR alignée ; 18/18 e2e verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CR-031</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Environnements</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>3 environnements GitHub : dev / int / prod</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>prod = ce que les clients reçoivent ; int = modifications client ; dev = développement. À créer à la préparation de la version finale.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Dépôt / CI</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>TRIAGED</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Plan écrit : docs/operations/environments.md. Déclenché par « version finale ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CR-032</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Versions pays</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>4 versions produit : Bahreïn, Tunisie, Qatar, Libye</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Le cadre permanent du produit. La couche pays existe (locales.js, CR-023/024) ; compléter curriculum/fériés/conformité par pays.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Couche pays</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CR-033</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>New feature</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Documentation produit</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Catalogue produit Excel : tous les éléments décrits</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Modules, services, rôles, comptes, pays, intégrations — web et mobile sur la même ligne.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>docs/quality</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Livré 2026-07-25 : Coreon-EDU_Product-Catalog.xlsx + générateur build-product-catalog.py (régénérable du code).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CR-034</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Intégrations</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Porte d'intégration système (import des données client)</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>La porte par laquelle un client apporte SES données : import OneRoster/CSV guidé (correspondance de colonnes, validation, rapport), puis API REST + webhooks.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Intégrations</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Demandé 2026-07-25. Après : l'hébergement backend. Export OneRoster + import JSON serveur existent déjà.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:T2"/>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -37535,7 +37535,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md.</t>
+          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md. · Volet fériés+hégirien livré 2026-07-25 : calendriers fériés par pays (FERIES_PAR_PAYS BH/QA/TN/LY, fetes.js suit locales.js) + date hégirienne Umm al-Qura native (Intl, zéro dép.) affichée BH/QA/LY (FeteCorner) ; i18n AR étendue ; 100/100 tests cœur.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -37634,12 +37634,12 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>Demandé 2026-07-25. Après : l'hébergement backend. Export OneRoster + import JSON serveur existent déjà.</t>
+          <t>Demandé 2026-07-25. Après : l'hébergement backend. Export OneRoster + import JSON serveur existent déjà. · Volet 1 livré 2026-07-25 : import CSV guidé /app/import (élèves+parents, personnel ; en-têtes FR/EN/AR/OneRoster ; rapprochement auto, validation, répétition générale, doublons=màj, annulation par photographie, journal des imports, identifiants provisoires) + docs/INTEGRATION.md. Reste : import serveur jour J (existe), API REST/webhooks après hébergement.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -37478,12 +37478,12 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>TRIAGED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>Plan écrit : docs/operations/environments.md. Déclenché par « version finale ».</t>
+          <t>Plan écrit : docs/operations/environments.md. Déclenché par « version finale ». · EN PLACE 2026-07-25 (version finale déclarée, 1er client BH) : branches dev/int + main=prod ; dev.edu + int.edu (Cloudflare Pages) ; envs.yml (dev rapide, int chaîne complète) ; environnements GitHub + protection main (checks requis) ; branche par défaut = dev ; secrets Cloudflare posés.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -37535,7 +37535,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md. · Volet fériés+hégirien livré 2026-07-25 : calendriers fériés par pays (FERIES_PAR_PAYS BH/QA/TN/LY, fetes.js suit locales.js) + date hégirienne Umm al-Qura native (Intl, zéro dép.) affichée BH/QA/LY (FeteCorner) ; i18n AR étendue ; 100/100 tests cœur.</t>
+          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md. · Volet fériés+hégirien livré 2026-07-25 : calendriers fériés par pays (FERIES_PAR_PAYS BH/QA/TN/LY, fetes.js suit locales.js) + date hégirienne Umm al-Qura native (Intl, zéro dép.) affichée BH/QA/LY (FeteCorner) ; i18n AR étendue ; 100/100 tests cœur. · Volet 2 livré 2026-07-26 : SEMAINE du pays (BH/QA/LY dim–jeu, week-end ven-sam — présence, emploi du temps, direct, cantine, paie), numéros d URGENCE du pays (999), pièce d identité par pack sur tous les écrans (CPR), documents officiels sans « Tunisie » en dur, alerte allergie FR/EN/AR, matières et météo du Golfe, assistant fondateur pays/langue + purge démo (école réelle).</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -32139,7 +32139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T149"/>
+  <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37640,6 +37640,120 @@
       <c r="T149" t="inlineStr">
         <is>
           <t>Demandé 2026-07-25. Après : l'hébergement backend. Export OneRoster + import JSON serveur existent déjà. · Volet 1 livré 2026-07-25 : import CSV guidé /app/import (élèves+parents, personnel ; en-têtes FR/EN/AR/OneRoster ; rapprochement auto, validation, répétition générale, doublons=màj, annulation par photographie, journal des imports, identifiants provisoires) + docs/INTEGRATION.md. Reste : import serveur jour J (existe), API REST/webhooks après hébergement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CR-035</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Gouvernance / provisionnement</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Le PAYS appartient à Kogia Group, pas à la direction</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>La direction gère son école, pas le contrat : pays/devise/langue par défaut se fixent au provisionnement par le compte Kogia Group ; l’école ne peut pas les changer.</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Livré 2026-07-26 : Localisation VERROUILLÉE pour la direction (note support), owner peut la modifier ; Setup pareil ; console Écoles = provisionnement réel (Pays au contrat, identifiants provisoires affichés UNE fois — fin du « identifiants envoyés » mensonger, mot de passe en clair retiré). Verrouillage serveur = avec l’hébergement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CR-036</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Anglais : troisième langue du produit</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Le Bahreïn travaille en anglais — il n’y avait pas d’anglais du tout.</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Tranche 1 livrée 2026-07-26 : locale EN + dictionnaire écorce (navigation, sections, rôles, niveaux — nommage Golfe KG1/KG2/Grade 1-6, connexion, coin des fêtes), sélecteur FR·EN·ع, dates en-GB, test de couverture AR+EN. Reste : les pages métier (~38) en EN et en AR, page par page.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -32139,7 +32139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T151"/>
+  <dimension ref="A1:T155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37535,7 +37535,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md. · Volet fériés+hégirien livré 2026-07-25 : calendriers fériés par pays (FERIES_PAR_PAYS BH/QA/TN/LY, fetes.js suit locales.js) + date hégirienne Umm al-Qura native (Intl, zéro dép.) affichée BH/QA/LY (FeteCorner) ; i18n AR étendue ; 100/100 tests cœur. · Volet 2 livré 2026-07-26 : SEMAINE du pays (BH/QA/LY dim–jeu, week-end ven-sam — présence, emploi du temps, direct, cantine, paie), numéros d URGENCE du pays (999), pièce d identité par pack sur tous les écrans (CPR), documents officiels sans « Tunisie » en dur, alerte allergie FR/EN/AR, matières et météo du Golfe, assistant fondateur pays/langue + purge démo (école réelle).</t>
+          <t>BH/QA/TN/LY présents dans locales.js ; manques Tier-1 par pays dans gap-analysis.md. · Volet fériés+hégirien livré 2026-07-25 : calendriers fériés par pays (FERIES_PAR_PAYS BH/QA/TN/LY, fetes.js suit locales.js) + date hégirienne Umm al-Qura native (Intl, zéro dép.) affichée BH/QA/LY (FeteCorner) ; i18n AR étendue ; 100/100 tests cœur. · Volet 2 livré 2026-07-26 : SEMAINE du pays (BH/QA/LY dim–jeu, week-end ven-sam — présence, emploi du temps, direct, cantine, paie), numéros d URGENCE du pays (999), pièce d identité par pack sur tous les écrans (CPR), documents officiels sans « Tunisie » en dur, alerte allergie FR/EN/AR, matières et météo du Golfe, assistant fondateur pays/langue + purge démo (école réelle). · Socle pays CONFORME (norme D3) : semaine dim–jeu, 999, CPR, PDPL, hégirien, fériés BH, décimales BHD. Réserves ouvertes : TVA 10 %/NBR, GOSI-EOSB, reporting MOE.</t>
         </is>
       </c>
     </row>
@@ -37634,12 +37634,12 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>Demandé 2026-07-25. Après : l'hébergement backend. Export OneRoster + import JSON serveur existent déjà. · Volet 1 livré 2026-07-25 : import CSV guidé /app/import (élèves+parents, personnel ; en-têtes FR/EN/AR/OneRoster ; rapprochement auto, validation, répétition générale, doublons=màj, annulation par photographie, journal des imports, identifiants provisoires) + docs/INTEGRATION.md. Reste : import serveur jour J (existe), API REST/webhooks après hébergement.</t>
+          <t>Demandé 2026-07-25. Après : l'hébergement backend. Export OneRoster + import JSON serveur existent déjà. · Volet 1 livré 2026-07-25 : import CSV guidé /app/import (élèves+parents, personnel ; en-têtes FR/EN/AR/OneRoster ; rapprochement auto, validation, répétition générale, doublons=màj, annulation par photographie, journal des imports, identifiants provisoires) + docs/INTEGRATION.md. Reste : import serveur jour J (existe), API REST/webhooks après hébergement. · Volet 1 accepté (norme D7 CONFORME) : import CSV guidé validé par diag.import.mjs 11/11. Restent en confort : ZIP d'export, API REST/webhooks après hébergement.</t>
         </is>
       </c>
     </row>
@@ -37753,7 +37753,215 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>Tranche 1 livrée 2026-07-26 : locale EN + dictionnaire écorce (navigation, sections, rôles, niveaux — nommage Golfe KG1/KG2/Grade 1-6, connexion, coin des fêtes), sélecteur FR·EN·ع, dates en-GB, test de couverture AR+EN. Reste : les pages métier (~38) en EN et en AR, page par page.</t>
+          <t>Tranche 1 livrée 2026-07-26 : locale EN + dictionnaire écorce (navigation, sections, rôles, niveaux — nommage Golfe KG1/KG2/Grade 1-6, connexion, coin des fêtes), sélecteur FR·EN·ع, dates en-GB, test de couverture AR+EN. Reste : les pages métier (~38) en EN et en AR, page par page. · Tranche 2 livrée 2026-07-26 : outil de mesure docs/quality/i18n-audit.py + BARRIÈRE CI (--gate, 40→60 %, jamais en arrière) ; +396 EN / +163 AR. Couverture mesurée : EN 62 %, AR 63 % (823 clés). Seuil d'acceptation client = 95 % (norme D4). Landing.jsx orphelin supprimé (133 clés mortes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CR-037</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>FAT / Othman</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Qualité / FAT</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Norme d'acceptation produit v1 + FAT exploratoire</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Créée 2026-07-26 : docs/quality/ACCEPTANCE-STANDARD-v1.md (10 domaines, critère + mesure exécutable + état) et 2 feuilles du classeur d'inventaire (FAT 2026-07-26, Norme d'acceptation v1). Prononcé v1.5.0 : PILOTE ACCOMPAGNÉ oui, LIVRAISON AUTONOME non.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CR-038</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>FAT / Othman</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Unifier les deux modèles d'argent (factures vs grille mensuelle)</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>FAT 2026-07-26 (norme D5) : /app/accounting et /app/finance peuvent se contredire pour le même élève ; location et activités encaissent sans reçu numéroté et n'atteignent pas la comptabilité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CR-039</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FAT / Othman</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Sécurité</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Journal d'audit immuable (qui a lu / modifié quoi)</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Norme D6 : exigence PDPL (BH) et INPDP (TN) — « qui a consulté ce dossier médical ? ». Absent. À faire avec l'hébergement serveur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CR-040</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FAT / Othman</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Exploitation</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Supervision de production (erreurs + disponibilité) et restauration répétée</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Norme D9 : aucune supervision aujourd'hui. Outils gratuits visés : Sentry (offre gratuite), UptimeRobot, plus une restauration de sauvegarde réellement exécutée et datée.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -37904,12 +37904,22 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>DONE — livré 2026-08-01</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>v1.7.0</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>core/src/audit.js : 9 natures de donnée sensible avec leur motif juridique ; lectures ET écritures journalisées (santé, personnes autorisées, fiche élève 360°, accidents, contrats &amp; paie, comptes, documents officiels, connexions et connexions REFUSÉES) ; clé de stockage séparée du blob de l'école ; chaîne d'empreintes qui nomme la première ligne altérée ; AUCUN chemin de suppression ; export CSV daté et lui-même journalisé ; /app/audit réservé à la Direction et à la plateforme. Preuves : 9 tests cœur (dont falsification, rotation comptée, purge démo non destructrice, injection de formule CSV) + e2e/parcours.audit.mjs (11 assertions, la consultation d'un dossier de santé apparaît bien au journal) + EN/AR 100 %.</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>Norme D6 : exigence PDPL (BH) et INPDP (TN) — « qui a consulté ce dossier médical ? ». Absent. À faire avec l'hébergement serveur.</t>
+          <t>RESTE : l'immuabilité est tamper-ÉVIDENTE, pas tamper-proof — le journal vit dans le navigateur. La garantie devient réelle avec D9 (table serveur en AJOUT SEUL). L'avant→après des valeurs est délibérément EXCLU des données sensibles : il ferait du journal un second dossier médical.</t>
         </is>
       </c>
     </row>
